--- a/outputs/signal_board_2026-05-04.xlsx
+++ b/outputs/signal_board_2026-05-04.xlsx
@@ -1753,12 +1753,12 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>93.0%</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>93.1% rostered</t>
+          <t>93.0% rostered</t>
         </is>
       </c>
       <c r="F17" s="9" t="inlineStr">
@@ -1982,12 +1982,12 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>89.9% rostered</t>
+          <t>89.7% rostered</t>
         </is>
       </c>
       <c r="F20" s="9" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>88.7%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>88.7% rostered</t>
+          <t>88.4% rostered</t>
         </is>
       </c>
       <c r="F21" s="9" t="inlineStr">
@@ -2134,12 +2134,12 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>84.4%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>84.5% rostered</t>
+          <t>84.4% rostered</t>
         </is>
       </c>
       <c r="F22" s="9" t="inlineStr">
@@ -2209,12 +2209,12 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>84.4%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>84.4% rostered</t>
+          <t>84.3% rostered</t>
         </is>
       </c>
       <c r="F23" s="9" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>75.1%</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>74.9% rostered</t>
+          <t>75.1% rostered</t>
         </is>
       </c>
       <c r="F25" s="9" t="inlineStr">
@@ -2671,12 +2671,12 @@
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>45.2% rostered</t>
+          <t>45.4% rostered</t>
         </is>
       </c>
       <c r="F29" s="9" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>43.1% rostered</t>
+          <t>43.6% rostered</t>
         </is>
       </c>
       <c r="F30" s="9" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>41.6% rostered</t>
+          <t>42.6% rostered</t>
         </is>
       </c>
       <c r="F31" s="9" t="inlineStr">
@@ -2979,12 +2979,12 @@
       </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>39.3% rostered</t>
+          <t>39.1% rostered</t>
         </is>
       </c>
       <c r="F33" s="9" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>36.2% rostered</t>
+          <t>36.3% rostered</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
@@ -3210,12 +3210,12 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>31.6% rostered</t>
+          <t>31.5% rostered</t>
         </is>
       </c>
       <c r="F36" s="9" t="inlineStr">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>16.3% rostered</t>
+          <t>16.2% rostered</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>16.2%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>16.2% rostered</t>
+          <t>15.8% rostered</t>
         </is>
       </c>
       <c r="F38" s="9" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>15.7% rostered</t>
+          <t>15.5% rostered</t>
         </is>
       </c>
       <c r="F39" s="9" t="inlineStr">
@@ -3518,12 +3518,12 @@
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>15.0% rostered</t>
+          <t>15.2% rostered</t>
         </is>
       </c>
       <c r="F40" s="9" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>11.4% rostered</t>
+          <t>11.3% rostered</t>
         </is>
       </c>
       <c r="F42" s="9" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>10.4% rostered</t>
+          <t>10.6% rostered</t>
         </is>
       </c>
       <c r="F43" s="9" t="inlineStr">
@@ -3965,12 +3965,12 @@
     <row r="46" ht="18" customHeight="1">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>Ezequiel Tovar</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
@@ -3995,59 +3995,59 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>.248</t>
+          <t>.239</t>
         </is>
       </c>
       <c r="H46" s="13" t="inlineStr">
         <is>
-          <t>.289</t>
+          <t>.281</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>+.041</t>
+          <t>+.042</t>
         </is>
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>.271</t>
+          <t>.225</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>.309</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L46" s="15" t="inlineStr">
         <is>
-          <t>-.038</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
         <is>
-          <t>+0.280</t>
+          <t>+0.267</t>
         </is>
       </c>
       <c r="N46" s="13" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="O46" s="13" t="inlineStr">
         <is>
-          <t>Slow starter (amplified)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>J. p. Crawford</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -4072,42 +4072,42 @@
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
-          <t>.239</t>
+          <t>.311</t>
         </is>
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>.281</t>
+          <t>.385</t>
         </is>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
-          <t>+.042</t>
+          <t>+.074</t>
         </is>
       </c>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>.225</t>
+          <t>.233</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>.298</t>
         </is>
       </c>
       <c r="L47" s="11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-.065</t>
         </is>
       </c>
       <c r="M47" s="10" t="inlineStr">
         <is>
-          <t>+0.267</t>
+          <t>+0.258</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>31</t>
         </is>
       </c>
       <c r="O47" s="8" t="inlineStr">
@@ -4119,12 +4119,12 @@
     <row r="48" ht="18" customHeight="1">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>J. p. Crawford</t>
+          <t>Ezequiel Tovar</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -4149,47 +4149,47 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>.311</t>
+          <t>.248</t>
         </is>
       </c>
       <c r="H48" s="13" t="inlineStr">
         <is>
-          <t>.385</t>
+          <t>.289</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>+.074</t>
+          <t>+.041</t>
         </is>
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>.233</t>
+          <t>.271</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>.298</t>
+          <t>.309</t>
         </is>
       </c>
       <c r="L48" s="15" t="inlineStr">
         <is>
-          <t>-.065</t>
+          <t>-.038</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
         <is>
-          <t>+0.258</t>
+          <t>+0.280</t>
         </is>
       </c>
       <c r="N48" s="13" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>25</t>
         </is>
       </c>
       <c r="O48" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Slow starter (amplified)</t>
         </is>
       </c>
     </row>
@@ -4211,12 +4211,12 @@
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>4.8% rostered</t>
+          <t>4.7% rostered</t>
         </is>
       </c>
       <c r="F49" s="9" t="inlineStr">
@@ -4365,12 +4365,12 @@
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>2.0% rostered</t>
+          <t>1.9% rostered</t>
         </is>
       </c>
       <c r="F51" s="9" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>83.3% rostered</t>
+          <t>83.2% rostered</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>79.1% rostered</t>
+          <t>78.9% rostered</t>
         </is>
       </c>
       <c r="F65" s="16" t="inlineStr">
@@ -5597,12 +5597,12 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>27.5% rostered</t>
+          <t>27.2% rostered</t>
         </is>
       </c>
       <c r="F67" s="16" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>8.0% rostered</t>
+          <t>7.9% rostered</t>
         </is>
       </c>
       <c r="F68" s="16" t="inlineStr">
@@ -5751,12 +5751,12 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>4.8% rostered</t>
+          <t>4.9% rostered</t>
         </is>
       </c>
       <c r="F69" s="16" t="inlineStr">
@@ -6365,12 +6365,12 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>97.7% rostered</t>
+          <t>97.6% rostered</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr">
@@ -6442,12 +6442,12 @@
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>95.7% rostered</t>
+          <t>95.8% rostered</t>
         </is>
       </c>
       <c r="F78" s="17" t="inlineStr">
@@ -6519,12 +6519,12 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>86.8% rostered</t>
+          <t>87.0% rostered</t>
         </is>
       </c>
       <c r="F79" s="17" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="D80" s="13" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E80" s="13" t="inlineStr">
         <is>
-          <t>85.8% rostered</t>
+          <t>85.7% rostered</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
@@ -6750,12 +6750,12 @@
       </c>
       <c r="D82" s="13" t="inlineStr">
         <is>
-          <t>83.5%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="E82" s="13" t="inlineStr">
         <is>
-          <t>83.5% rostered</t>
+          <t>83.4% rostered</t>
         </is>
       </c>
       <c r="F82" s="17" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>83.4%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>83.4% rostered</t>
+          <t>83.3% rostered</t>
         </is>
       </c>
       <c r="F83" s="17" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="D84" s="13" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="E84" s="13" t="inlineStr">
         <is>
-          <t>80.3% rostered</t>
+          <t>80.2% rostered</t>
         </is>
       </c>
       <c r="F84" s="17" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>65.1% rostered</t>
+          <t>64.9% rostered</t>
         </is>
       </c>
       <c r="F85" s="17" t="inlineStr">
@@ -7056,12 +7056,12 @@
       </c>
       <c r="D86" s="13" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="E86" s="13" t="inlineStr">
         <is>
-          <t>62.9% rostered</t>
+          <t>61.9% rostered</t>
         </is>
       </c>
       <c r="F86" s="17" t="inlineStr">
@@ -7133,12 +7133,12 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>52.7% rostered</t>
+          <t>52.6% rostered</t>
         </is>
       </c>
       <c r="F87" s="17" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="D88" s="13" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>43.3% rostered</t>
+          <t>43.2% rostered</t>
         </is>
       </c>
       <c r="F88" s="17" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="D90" s="13" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>27.8% rostered</t>
+          <t>28.1% rostered</t>
         </is>
       </c>
       <c r="F90" s="17" t="inlineStr">
@@ -7441,12 +7441,12 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>24.0% rostered</t>
+          <t>23.6% rostered</t>
         </is>
       </c>
       <c r="F91" s="17" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>21.7% rostered</t>
+          <t>22.2% rostered</t>
         </is>
       </c>
       <c r="F93" s="17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="D94" s="13" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="E94" s="13" t="inlineStr">
         <is>
-          <t>12.4% rostered</t>
+          <t>12.7% rostered</t>
         </is>
       </c>
       <c r="F94" s="17" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>8.0% rostered</t>
+          <t>8.1% rostered</t>
         </is>
       </c>
       <c r="F95" s="17" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="D96" s="13" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>8.0%</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>7.7% rostered</t>
+          <t>8.0% rostered</t>
         </is>
       </c>
       <c r="F96" s="17" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>4.4% rostered</t>
+          <t>4.3% rostered</t>
         </is>
       </c>
       <c r="F99" s="17" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="D100" s="13" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>3.7% rostered</t>
+          <t>3.8% rostered</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>1.5% rostered</t>
+          <t>1.7% rostered</t>
         </is>
       </c>
       <c r="F101" s="17" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="D106" s="13" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>99.3% rostered</t>
+          <t>99.2% rostered</t>
         </is>
       </c>
       <c r="F106" s="18" t="inlineStr">
@@ -9133,12 +9133,12 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>88.2% rostered</t>
+          <t>88.5% rostered</t>
         </is>
       </c>
       <c r="F113" s="18" t="inlineStr">
@@ -9285,12 +9285,12 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>76.8% rostered</t>
+          <t>77.1% rostered</t>
         </is>
       </c>
       <c r="F115" s="18" t="inlineStr">
@@ -9362,12 +9362,12 @@
       </c>
       <c r="D116" s="13" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
-          <t>72.7% rostered</t>
+          <t>73.0% rostered</t>
         </is>
       </c>
       <c r="F116" s="18" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>72.4% rostered</t>
+          <t>72.5% rostered</t>
         </is>
       </c>
       <c r="F117" s="18" t="inlineStr">
@@ -9516,12 +9516,12 @@
       </c>
       <c r="D118" s="13" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="E118" s="13" t="inlineStr">
         <is>
-          <t>72.0% rostered</t>
+          <t>71.6% rostered</t>
         </is>
       </c>
       <c r="F118" s="18" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="D120" s="13" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="E120" s="13" t="inlineStr">
         <is>
-          <t>47.1% rostered</t>
+          <t>47.3% rostered</t>
         </is>
       </c>
       <c r="F120" s="18" t="inlineStr">
@@ -9747,12 +9747,12 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>39.8% rostered</t>
+          <t>40.2% rostered</t>
         </is>
       </c>
       <c r="F121" s="18" t="inlineStr">
@@ -9824,12 +9824,12 @@
       </c>
       <c r="D122" s="13" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.5%</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>28.6% rostered</t>
+          <t>28.5% rostered</t>
         </is>
       </c>
       <c r="F122" s="18" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
-          <t>24.7% rostered</t>
+          <t>24.2% rostered</t>
         </is>
       </c>
       <c r="F124" s="18" t="inlineStr">
@@ -10055,12 +10055,12 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>16.8%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>16.8% rostered</t>
+          <t>16.7% rostered</t>
         </is>
       </c>
       <c r="F125" s="18" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="D126" s="13" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>11.5% rostered</t>
+          <t>11.4% rostered</t>
         </is>
       </c>
       <c r="F126" s="18" t="inlineStr">
@@ -10194,12 +10194,12 @@
     <row r="127" ht="18" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Casey Schmitt</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
@@ -10209,12 +10209,12 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>9.9% rostered</t>
+          <t>10.3% rostered</t>
         </is>
       </c>
       <c r="F127" s="18" t="inlineStr">
@@ -10224,59 +10224,59 @@
       </c>
       <c r="G127" s="8" t="inlineStr">
         <is>
-          <t>.395</t>
+          <t>.382</t>
         </is>
       </c>
       <c r="H127" s="8" t="inlineStr">
         <is>
-          <t>.346</t>
+          <t>.374</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>-.049</t>
+          <t>-.008</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>.381</t>
+          <t>.368</t>
         </is>
       </c>
       <c r="K127" s="8" t="inlineStr">
         <is>
-          <t>.280</t>
+          <t>.278</t>
         </is>
       </c>
       <c r="L127" s="10" t="inlineStr">
         <is>
-          <t>+.101</t>
+          <t>+.090</t>
         </is>
       </c>
       <c r="M127" s="11" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="N127" s="8" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O127" s="8" t="inlineStr">
         <is>
-          <t>Second half fader (amplified)</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="128" ht="18" customHeight="1">
       <c r="A128" s="12" t="inlineStr">
         <is>
-          <t>Casey Schmitt</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="B128" s="13" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C128" s="13" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="D128" s="13" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="E128" s="13" t="inlineStr">
         <is>
-          <t>9.9% rostered</t>
+          <t>10.1% rostered</t>
         </is>
       </c>
       <c r="F128" s="18" t="inlineStr">
@@ -10301,47 +10301,47 @@
       </c>
       <c r="G128" s="13" t="inlineStr">
         <is>
-          <t>.382</t>
+          <t>.395</t>
         </is>
       </c>
       <c r="H128" s="13" t="inlineStr">
         <is>
-          <t>.374</t>
+          <t>.346</t>
         </is>
       </c>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>-.008</t>
+          <t>-.049</t>
         </is>
       </c>
       <c r="J128" s="13" t="inlineStr">
         <is>
-          <t>.368</t>
+          <t>.381</t>
         </is>
       </c>
       <c r="K128" s="13" t="inlineStr">
         <is>
-          <t>.278</t>
+          <t>.280</t>
         </is>
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>+.090</t>
+          <t>+.101</t>
         </is>
       </c>
       <c r="M128" s="15" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="N128" s="13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="O128" s="13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Second half fader (amplified)</t>
         </is>
       </c>
     </row>
@@ -10363,12 +10363,12 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>9.6% rostered</t>
+          <t>9.5% rostered</t>
         </is>
       </c>
       <c r="F129" s="18" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="D130" s="13" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>7.2% rostered</t>
+          <t>7.1% rostered</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>6.9% rostered</t>
+          <t>6.8% rostered</t>
         </is>
       </c>
       <c r="F131" s="18" t="inlineStr">
@@ -10671,12 +10671,12 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>6.5% rostered</t>
+          <t>6.4% rostered</t>
         </is>
       </c>
       <c r="F133" s="18" t="inlineStr">
@@ -10748,12 +10748,12 @@
       </c>
       <c r="D134" s="13" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
-          <t>6.5% rostered</t>
+          <t>6.4% rostered</t>
         </is>
       </c>
       <c r="F134" s="18" t="inlineStr">
@@ -10825,12 +10825,12 @@
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>6.5% rostered</t>
+          <t>6.4% rostered</t>
         </is>
       </c>
       <c r="F135" s="18" t="inlineStr">
@@ -10902,12 +10902,12 @@
       </c>
       <c r="D136" s="13" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="E136" s="13" t="inlineStr">
         <is>
-          <t>5.7% rostered</t>
+          <t>5.8% rostered</t>
         </is>
       </c>
       <c r="F136" s="18" t="inlineStr">
@@ -10964,12 +10964,12 @@
     <row r="137" ht="18" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Nick Gonzales</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="C137" s="8" t="inlineStr">
@@ -10994,42 +10994,42 @@
       </c>
       <c r="G137" s="8" t="inlineStr">
         <is>
-          <t>.344</t>
+          <t>.342</t>
         </is>
       </c>
       <c r="H137" s="8" t="inlineStr">
         <is>
-          <t>.329</t>
+          <t>.341</t>
         </is>
       </c>
       <c r="I137" s="11" t="inlineStr">
         <is>
-          <t>-.015</t>
+          <t>-.001</t>
         </is>
       </c>
       <c r="J137" s="8" t="inlineStr">
         <is>
-          <t>.362</t>
+          <t>.400</t>
         </is>
       </c>
       <c r="K137" s="8" t="inlineStr">
         <is>
-          <t>.286</t>
+          <t>.308</t>
         </is>
       </c>
       <c r="L137" s="10" t="inlineStr">
         <is>
-          <t>+.076</t>
+          <t>+.092</t>
         </is>
       </c>
       <c r="M137" s="11" t="inlineStr">
         <is>
-          <t>-0.217</t>
+          <t>-0.324</t>
         </is>
       </c>
       <c r="N137" s="8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="O137" s="8" t="inlineStr">
@@ -11041,12 +11041,12 @@
     <row r="138" ht="18" customHeight="1">
       <c r="A138" s="12" t="inlineStr">
         <is>
-          <t>Nick Gonzales</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="B138" s="13" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="C138" s="13" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="D138" s="13" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="E138" s="13" t="inlineStr">
         <is>
-          <t>4.2% rostered</t>
+          <t>4.3% rostered</t>
         </is>
       </c>
       <c r="F138" s="18" t="inlineStr">
@@ -11071,42 +11071,42 @@
       </c>
       <c r="G138" s="13" t="inlineStr">
         <is>
-          <t>.342</t>
+          <t>.344</t>
         </is>
       </c>
       <c r="H138" s="13" t="inlineStr">
         <is>
-          <t>.341</t>
+          <t>.329</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>-.001</t>
+          <t>-.015</t>
         </is>
       </c>
       <c r="J138" s="13" t="inlineStr">
         <is>
-          <t>.400</t>
+          <t>.362</t>
         </is>
       </c>
       <c r="K138" s="13" t="inlineStr">
         <is>
-          <t>.308</t>
+          <t>.286</t>
         </is>
       </c>
       <c r="L138" s="14" t="inlineStr">
         <is>
-          <t>+.092</t>
+          <t>+.076</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>-0.324</t>
+          <t>-0.217</t>
         </is>
       </c>
       <c r="N138" s="13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="O138" s="13" t="inlineStr">
@@ -11210,12 +11210,12 @@
       </c>
       <c r="D140" s="13" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E140" s="13" t="inlineStr">
         <is>
-          <t>2.5% rostered</t>
+          <t>2.4% rostered</t>
         </is>
       </c>
       <c r="F140" s="18" t="inlineStr">
@@ -11672,12 +11672,12 @@
       </c>
       <c r="D146" s="13" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
-          <t>0.1% rostered</t>
+          <t>0.2% rostered</t>
         </is>
       </c>
       <c r="F146" s="18" t="inlineStr">
@@ -11919,12 +11919,12 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>95.9%</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
-          <t>96.0% rostered</t>
+          <t>95.9% rostered</t>
         </is>
       </c>
       <c r="F5" s="9" t="inlineStr">
@@ -12012,12 +12012,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>95.9%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>95.9% rostered</t>
+          <t>95.3% rostered</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
@@ -12105,12 +12105,12 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>91.5% rostered</t>
+          <t>91.6% rostered</t>
         </is>
       </c>
       <c r="F7" s="9" t="inlineStr">
@@ -12198,12 +12198,12 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>26.4% rostered</t>
+          <t>26.7% rostered</t>
         </is>
       </c>
       <c r="F8" s="9" t="inlineStr">
@@ -12291,12 +12291,12 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>12.0% rostered</t>
+          <t>11.8% rostered</t>
         </is>
       </c>
       <c r="F9" s="9" t="inlineStr">
@@ -12477,12 +12477,12 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>4.8% rostered</t>
+          <t>4.7% rostered</t>
         </is>
       </c>
       <c r="F11" s="9" t="inlineStr">
@@ -12663,12 +12663,12 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>72.9% rostered</t>
+          <t>72.3% rostered</t>
         </is>
       </c>
       <c r="F13" s="16" t="inlineStr">
@@ -12756,12 +12756,12 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>48.3% rostered</t>
+          <t>48.1% rostered</t>
         </is>
       </c>
       <c r="F14" s="16" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>3.4% rostered</t>
+          <t>3.5% rostered</t>
         </is>
       </c>
       <c r="F16" s="16" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>92.2% rostered</t>
+          <t>92.3% rostered</t>
         </is>
       </c>
       <c r="F19" s="17" t="inlineStr">
@@ -13314,12 +13314,12 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>87.4%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>87.4% rostered</t>
+          <t>87.1% rostered</t>
         </is>
       </c>
       <c r="F20" s="17" t="inlineStr">
@@ -13407,12 +13407,12 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.3%</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>78.1% rostered</t>
+          <t>78.3% rostered</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -13500,12 +13500,12 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>74.3% rostered</t>
+          <t>74.7% rostered</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -13593,12 +13593,12 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>57.3% rostered</t>
+          <t>57.2% rostered</t>
         </is>
       </c>
       <c r="F23" s="17" t="inlineStr">
@@ -13686,12 +13686,12 @@
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>40.5% rostered</t>
+          <t>40.4% rostered</t>
         </is>
       </c>
       <c r="F24" s="17" t="inlineStr">
@@ -13779,12 +13779,12 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>34.4% rostered</t>
+          <t>34.2% rostered</t>
         </is>
       </c>
       <c r="F25" s="17" t="inlineStr">
@@ -13872,12 +13872,12 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>22.7% rostered</t>
+          <t>21.6% rostered</t>
         </is>
       </c>
       <c r="F26" s="17" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>20.3% rostered</t>
+          <t>21.5% rostered</t>
         </is>
       </c>
       <c r="F27" s="17" t="inlineStr">
@@ -14709,12 +14709,12 @@
       </c>
       <c r="D35" s="8" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>89.2% rostered</t>
+          <t>89.3% rostered</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
@@ -14802,12 +14802,12 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>77.3% rostered</t>
+          <t>77.2% rostered</t>
         </is>
       </c>
       <c r="F36" s="18" t="inlineStr">
@@ -14895,12 +14895,12 @@
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>76.9% rostered</t>
+          <t>76.2% rostered</t>
         </is>
       </c>
       <c r="F37" s="18" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>72.4% rostered</t>
+          <t>72.5% rostered</t>
         </is>
       </c>
       <c r="F38" s="18" t="inlineStr">
@@ -15066,27 +15066,27 @@
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Justin Wrobleski</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>36.3</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>61.0%</t>
         </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>60.0% rostered</t>
+          <t>61.0% rostered</t>
         </is>
       </c>
       <c r="F39" s="18" t="inlineStr">
@@ -15096,47 +15096,47 @@
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="I39" s="8" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
         <is>
-          <t>.222</t>
+          <t>.303</t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t>.300</t>
+          <t>.303</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="N39" s="11" t="inlineStr">
         <is>
-          <t>-0.440</t>
+          <t>-0.306</t>
         </is>
       </c>
       <c r="O39" s="8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="P39" s="8" t="inlineStr">
@@ -15159,27 +15159,27 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Justin Wrobleski</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>36.3</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>58.6% rostered</t>
+          <t>59.6% rostered</t>
         </is>
       </c>
       <c r="F40" s="18" t="inlineStr">
@@ -15189,47 +15189,47 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="J40" s="15" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>.303</t>
+          <t>.222</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
         <is>
-          <t>.303</t>
+          <t>.300</t>
         </is>
       </c>
       <c r="M40" s="13" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="N40" s="15" t="inlineStr">
         <is>
-          <t>-0.306</t>
+          <t>-0.440</t>
         </is>
       </c>
       <c r="O40" s="13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="P40" s="13" t="inlineStr">
@@ -15267,12 +15267,12 @@
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>57.7% rostered</t>
+          <t>58.4% rostered</t>
         </is>
       </c>
       <c r="F41" s="18" t="inlineStr">
@@ -15360,12 +15360,12 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>56.1% rostered</t>
+          <t>57.2% rostered</t>
         </is>
       </c>
       <c r="F42" s="18" t="inlineStr">
@@ -15453,12 +15453,12 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>53.0% rostered</t>
+          <t>53.2% rostered</t>
         </is>
       </c>
       <c r="F43" s="18" t="inlineStr">
@@ -15546,12 +15546,12 @@
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>36.5% rostered</t>
+          <t>40.2% rostered</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>31.9% rostered</t>
+          <t>31.5% rostered</t>
         </is>
       </c>
       <c r="F45" s="18" t="inlineStr">
@@ -15732,12 +15732,12 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.1%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>25.3% rostered</t>
+          <t>25.1% rostered</t>
         </is>
       </c>
       <c r="F46" s="18" t="inlineStr">
@@ -15825,12 +15825,12 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>21.1% rostered</t>
+          <t>20.7% rostered</t>
         </is>
       </c>
       <c r="F47" s="18" t="inlineStr">
@@ -15918,12 +15918,12 @@
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>18.5% rostered</t>
+          <t>17.2% rostered</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
@@ -16104,12 +16104,12 @@
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
         <is>
-          <t>9.8% rostered</t>
+          <t>10.5% rostered</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
@@ -16182,27 +16182,27 @@
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Aaron Civale</t>
+          <t>Tomoyuki Sugano</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>36.0</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>9.3% rostered</t>
+          <t>9.5% rostered</t>
         </is>
       </c>
       <c r="F51" s="18" t="inlineStr">
@@ -16212,52 +16212,52 @@
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="I51" s="8" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>5.48</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-1.76</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
         <is>
-          <t>.304</t>
+          <t>.240</t>
         </is>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
-          <t>.294</t>
+          <t>.324</t>
         </is>
       </c>
       <c r="M51" s="8" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="N51" s="11" t="inlineStr">
         <is>
-          <t>-0.236</t>
+          <t>-0.396</t>
         </is>
       </c>
       <c r="O51" s="8" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>37</t>
         </is>
       </c>
       <c r="P51" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q51" s="8" t="inlineStr">
@@ -16290,12 +16290,12 @@
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>9.3% rostered</t>
+          <t>9.4% rostered</t>
         </is>
       </c>
       <c r="F52" s="18" t="inlineStr">
@@ -16368,27 +16368,27 @@
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Tomoyuki Sugano</t>
+          <t>Aaron Civale</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>36.0</t>
         </is>
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>8.2%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>8.2% rostered</t>
+          <t>8.8% rostered</t>
         </is>
       </c>
       <c r="F53" s="18" t="inlineStr">
@@ -16398,52 +16398,52 @@
       </c>
       <c r="G53" s="8" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="I53" s="8" t="inlineStr">
         <is>
-          <t>5.48</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
         <is>
-          <t>.240</t>
+          <t>.304</t>
         </is>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
-          <t>.324</t>
+          <t>.294</t>
         </is>
       </c>
       <c r="M53" s="8" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="N53" s="11" t="inlineStr">
         <is>
-          <t>-0.396</t>
+          <t>-0.236</t>
         </is>
       </c>
       <c r="O53" s="8" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="P53" s="8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q53" s="8" t="inlineStr">
@@ -16569,12 +16569,12 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>0.3% rostered</t>
+          <t>0.4% rostered</t>
         </is>
       </c>
       <c r="F55" s="18" t="inlineStr">
@@ -17307,12 +17307,12 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>99.3% rostered</t>
+          <t>99.2% rostered</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -17369,12 +17369,12 @@
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>98.9% rostered</t>
+          <t>99.0% rostered</t>
         </is>
       </c>
       <c r="F13" s="24" t="inlineStr">
@@ -17493,12 +17493,12 @@
       </c>
       <c r="D15" s="24" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>98.4% rostered</t>
+          <t>98.5% rostered</t>
         </is>
       </c>
       <c r="F15" s="24" t="inlineStr">
@@ -17617,12 +17617,12 @@
       </c>
       <c r="D17" s="24" t="inlineStr">
         <is>
-          <t>97.7%</t>
+          <t>97.6%</t>
         </is>
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>97.7% rostered</t>
+          <t>97.6% rostered</t>
         </is>
       </c>
       <c r="F17" s="24" t="inlineStr">
@@ -17803,12 +17803,12 @@
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>96.4% rostered</t>
+          <t>96.3% rostered</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
@@ -17927,12 +17927,12 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>95.7% rostered</t>
+          <t>95.8% rostered</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
@@ -18175,12 +18175,12 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>88.2% rostered</t>
+          <t>88.5% rostered</t>
         </is>
       </c>
       <c r="F26" s="13" t="inlineStr">
@@ -18237,12 +18237,12 @@
       </c>
       <c r="D27" s="24" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>88.0% rostered</t>
+          <t>88.2% rostered</t>
         </is>
       </c>
       <c r="F27" s="24" t="inlineStr">
@@ -18299,12 +18299,12 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>87.8% rostered</t>
+          <t>87.7% rostered</t>
         </is>
       </c>
       <c r="F28" s="13" t="inlineStr">
@@ -18423,12 +18423,12 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>87.0%</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>86.8% rostered</t>
+          <t>87.0% rostered</t>
         </is>
       </c>
       <c r="F30" s="13" t="inlineStr">
@@ -18470,17 +18470,17 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="23" t="inlineStr">
         <is>
-          <t>Taylor Ward</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="B31" s="24" t="inlineStr">
         <is>
-          <t>BAL</t>
-        </is>
-      </c>
-      <c r="C31" s="27" t="inlineStr">
-        <is>
-          <t>Monitor</t>
+          <t>MIA</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="D31" s="24" t="inlineStr">
@@ -18495,54 +18495,54 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>.394</t>
+          <t>.385</t>
         </is>
       </c>
       <c r="G31" s="24" t="inlineStr">
         <is>
-          <t>.390</t>
+          <t>.438</t>
         </is>
       </c>
       <c r="H31" s="24" t="inlineStr">
         <is>
-          <t>.361</t>
+          <t>.271</t>
         </is>
       </c>
       <c r="I31" s="24" t="inlineStr">
         <is>
-          <t>.301</t>
-        </is>
-      </c>
-      <c r="J31" s="28" t="inlineStr">
-        <is>
-          <t>-0.127</t>
-        </is>
-      </c>
-      <c r="K31" s="17" t="inlineStr">
-        <is>
-          <t>Slight sell</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" s="26" t="inlineStr">
+        <is>
+          <t>+0.082</t>
+        </is>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="L31" s="24" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Taylor Ward</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>MIA</t>
-        </is>
-      </c>
-      <c r="C32" s="25" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
+          <t>BAL</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="inlineStr">
+        <is>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
@@ -18557,37 +18557,37 @@
       </c>
       <c r="F32" s="13" t="inlineStr">
         <is>
-          <t>.385</t>
+          <t>.394</t>
         </is>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>.438</t>
+          <t>.390</t>
         </is>
       </c>
       <c r="H32" s="13" t="inlineStr">
         <is>
-          <t>.271</t>
+          <t>.361</t>
         </is>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J32" s="14" t="inlineStr">
-        <is>
-          <t>+0.082</t>
-        </is>
-      </c>
-      <c r="K32" s="7" t="inlineStr">
-        <is>
-          <t>Neutral</t>
+          <t>.301</t>
+        </is>
+      </c>
+      <c r="J32" s="15" t="inlineStr">
+        <is>
+          <t>-0.127</t>
+        </is>
+      </c>
+      <c r="K32" s="17" t="inlineStr">
+        <is>
+          <t>Slight sell</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -18656,12 +18656,12 @@
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Ian Happ</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C34" s="27" t="inlineStr">
@@ -18681,49 +18681,49 @@
       </c>
       <c r="F34" s="13" t="inlineStr">
         <is>
-          <t>.376</t>
+          <t>.402</t>
         </is>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>.382</t>
+          <t>.375</t>
         </is>
       </c>
       <c r="H34" s="13" t="inlineStr">
         <is>
-          <t>.365</t>
+          <t>.300</t>
         </is>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>.309</t>
+          <t>.301</t>
         </is>
       </c>
       <c r="J34" s="15" t="inlineStr">
         <is>
-          <t>-0.148</t>
-        </is>
-      </c>
-      <c r="K34" s="17" t="inlineStr">
-        <is>
-          <t>Slight sell</t>
+          <t>-0.058</t>
+        </is>
+      </c>
+      <c r="K34" s="7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>Ian Happ</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="B35" s="24" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="C35" s="27" t="inlineStr">
@@ -18733,47 +18733,47 @@
       </c>
       <c r="D35" s="24" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>83.4%</t>
         </is>
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>83.2% rostered</t>
+          <t>83.4% rostered</t>
         </is>
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>.402</t>
+          <t>.376</t>
         </is>
       </c>
       <c r="G35" s="24" t="inlineStr">
         <is>
-          <t>.375</t>
+          <t>.382</t>
         </is>
       </c>
       <c r="H35" s="24" t="inlineStr">
         <is>
-          <t>.300</t>
+          <t>.365</t>
         </is>
       </c>
       <c r="I35" s="24" t="inlineStr">
         <is>
-          <t>.301</t>
+          <t>.309</t>
         </is>
       </c>
       <c r="J35" s="28" t="inlineStr">
         <is>
-          <t>-0.058</t>
-        </is>
-      </c>
-      <c r="K35" s="7" t="inlineStr">
-        <is>
-          <t>Neutral</t>
+          <t>-0.148</t>
+        </is>
+      </c>
+      <c r="K35" s="17" t="inlineStr">
+        <is>
+          <t>Slight sell</t>
         </is>
       </c>
       <c r="L35" s="24" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -18795,12 +18795,12 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>82.7% rostered</t>
+          <t>82.8% rostered</t>
         </is>
       </c>
       <c r="F36" s="13" t="inlineStr">
@@ -18857,12 +18857,12 @@
       </c>
       <c r="D37" s="24" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>80.8% rostered</t>
+          <t>81.0% rostered</t>
         </is>
       </c>
       <c r="F37" s="24" t="inlineStr">
@@ -18919,12 +18919,12 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>80.3% rostered</t>
+          <t>80.2% rostered</t>
         </is>
       </c>
       <c r="F38" s="13" t="inlineStr">
@@ -18981,12 +18981,12 @@
       </c>
       <c r="D39" s="24" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>78.1% rostered</t>
+          <t>78.0% rostered</t>
         </is>
       </c>
       <c r="F39" s="24" t="inlineStr">
@@ -19028,124 +19028,124 @@
     <row r="40" ht="18" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>Christian Walker</t>
+          <t>Chase Delauter</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>HOU</t>
-        </is>
-      </c>
-      <c r="C40" s="27" t="inlineStr">
-        <is>
-          <t>Monitor</t>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>76.8% rostered</t>
+          <t>77.6% rostered</t>
         </is>
       </c>
       <c r="F40" s="13" t="inlineStr">
         <is>
-          <t>.433</t>
+          <t>.389</t>
         </is>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>.408</t>
+          <t>.393</t>
         </is>
       </c>
       <c r="H40" s="13" t="inlineStr">
         <is>
-          <t>.341</t>
+          <t>.297</t>
         </is>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>.297</t>
-        </is>
-      </c>
-      <c r="J40" s="15" t="inlineStr">
-        <is>
-          <t>-0.238</t>
-        </is>
-      </c>
-      <c r="K40" s="18" t="inlineStr">
-        <is>
-          <t>Sell high</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J40" s="14" t="inlineStr">
+        <is>
+          <t>+0.028</t>
+        </is>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="L40" s="13" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="23" t="inlineStr">
         <is>
-          <t>Chase Delauter</t>
+          <t>Christian Walker</t>
         </is>
       </c>
       <c r="B41" s="24" t="inlineStr">
         <is>
-          <t>CLE</t>
-        </is>
-      </c>
-      <c r="C41" s="25" t="inlineStr">
-        <is>
-          <t>Confirmed</t>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="C41" s="27" t="inlineStr">
+        <is>
+          <t>Monitor</t>
         </is>
       </c>
       <c r="D41" s="24" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>76.8% rostered</t>
+          <t>77.1% rostered</t>
         </is>
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>.389</t>
+          <t>.433</t>
         </is>
       </c>
       <c r="G41" s="24" t="inlineStr">
         <is>
-          <t>.393</t>
+          <t>.408</t>
         </is>
       </c>
       <c r="H41" s="24" t="inlineStr">
         <is>
+          <t>.341</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
           <t>.297</t>
         </is>
       </c>
-      <c r="I41" s="24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J41" s="26" t="inlineStr">
-        <is>
-          <t>+0.028</t>
-        </is>
-      </c>
-      <c r="K41" s="7" t="inlineStr">
-        <is>
-          <t>Neutral</t>
+      <c r="J41" s="28" t="inlineStr">
+        <is>
+          <t>-0.238</t>
+        </is>
+      </c>
+      <c r="K41" s="18" t="inlineStr">
+        <is>
+          <t>Sell high</t>
         </is>
       </c>
       <c r="L41" s="24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -19167,12 +19167,12 @@
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>72.7% rostered</t>
+          <t>73.0% rostered</t>
         </is>
       </c>
       <c r="F42" s="13" t="inlineStr">
@@ -19229,12 +19229,12 @@
       </c>
       <c r="D43" s="24" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>72.4% rostered</t>
+          <t>72.5% rostered</t>
         </is>
       </c>
       <c r="F43" s="24" t="inlineStr">
@@ -19353,12 +19353,12 @@
       </c>
       <c r="D45" s="24" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>62.1% rostered</t>
+          <t>62.0% rostered</t>
         </is>
       </c>
       <c r="F45" s="24" t="inlineStr">
@@ -19415,12 +19415,12 @@
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>58.6% rostered</t>
+          <t>58.5% rostered</t>
         </is>
       </c>
       <c r="F46" s="13" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="D47" s="24" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>53.9% rostered</t>
+          <t>56.5% rostered</t>
         </is>
       </c>
       <c r="F47" s="24" t="inlineStr">
@@ -19539,12 +19539,12 @@
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>53.8% rostered</t>
+          <t>53.9% rostered</t>
         </is>
       </c>
       <c r="F48" s="13" t="inlineStr">
@@ -19601,12 +19601,12 @@
       </c>
       <c r="D49" s="24" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>41.6% rostered</t>
+          <t>42.6% rostered</t>
         </is>
       </c>
       <c r="F49" s="24" t="inlineStr">
@@ -19725,12 +19725,12 @@
       </c>
       <c r="D51" s="24" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>27.8% rostered</t>
+          <t>28.1% rostered</t>
         </is>
       </c>
       <c r="F51" s="24" t="inlineStr">
@@ -19787,12 +19787,12 @@
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
         <is>
-          <t>24.7% rostered</t>
+          <t>24.2% rostered</t>
         </is>
       </c>
       <c r="F52" s="13" t="inlineStr">
@@ -19849,12 +19849,12 @@
       </c>
       <c r="D53" s="24" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>21.5% rostered</t>
+          <t>21.7% rostered</t>
         </is>
       </c>
       <c r="F53" s="24" t="inlineStr">
@@ -19911,12 +19911,12 @@
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
         <is>
-          <t>12.4% rostered</t>
+          <t>12.7% rostered</t>
         </is>
       </c>
       <c r="F54" s="13" t="inlineStr">
@@ -19973,12 +19973,12 @@
       </c>
       <c r="D55" s="24" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>11.5% rostered</t>
+          <t>11.4% rostered</t>
         </is>
       </c>
       <c r="F55" s="24" t="inlineStr">
@@ -20020,12 +20020,12 @@
     <row r="56" ht="18" customHeight="1">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>Carson Kelly</t>
+          <t>Casey Schmitt</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="C56" s="27" t="inlineStr">
@@ -20035,37 +20035,37 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>9.9% rostered</t>
+          <t>10.3% rostered</t>
         </is>
       </c>
       <c r="F56" s="13" t="inlineStr">
         <is>
-          <t>.395</t>
+          <t>.382</t>
         </is>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>.346</t>
+          <t>.374</t>
         </is>
       </c>
       <c r="H56" s="13" t="inlineStr">
         <is>
-          <t>.381</t>
+          <t>.368</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>.280</t>
+          <t>.278</t>
         </is>
       </c>
       <c r="J56" s="15" t="inlineStr">
         <is>
-          <t>-0.240</t>
+          <t>-0.290</t>
         </is>
       </c>
       <c r="K56" s="18" t="inlineStr">
@@ -20075,19 +20075,19 @@
       </c>
       <c r="L56" s="13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
       <c r="A57" s="23" t="inlineStr">
         <is>
-          <t>Casey Schmitt</t>
+          <t>Carson Kelly</t>
         </is>
       </c>
       <c r="B57" s="24" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="C57" s="27" t="inlineStr">
@@ -20097,37 +20097,37 @@
       </c>
       <c r="D57" s="24" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>9.9% rostered</t>
+          <t>10.1% rostered</t>
         </is>
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>.382</t>
+          <t>.395</t>
         </is>
       </c>
       <c r="G57" s="24" t="inlineStr">
         <is>
-          <t>.374</t>
+          <t>.346</t>
         </is>
       </c>
       <c r="H57" s="24" t="inlineStr">
         <is>
-          <t>.368</t>
+          <t>.381</t>
         </is>
       </c>
       <c r="I57" s="24" t="inlineStr">
         <is>
-          <t>.278</t>
+          <t>.280</t>
         </is>
       </c>
       <c r="J57" s="28" t="inlineStr">
         <is>
-          <t>-0.290</t>
+          <t>-0.240</t>
         </is>
       </c>
       <c r="K57" s="18" t="inlineStr">
@@ -20137,7 +20137,7 @@
       </c>
       <c r="L57" s="24" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -20159,12 +20159,12 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
         <is>
-          <t>6.5% rostered</t>
+          <t>6.4% rostered</t>
         </is>
       </c>
       <c r="F58" s="13" t="inlineStr">
@@ -20221,12 +20221,12 @@
       </c>
       <c r="D59" s="24" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>6.0% rostered</t>
+          <t>5.8% rostered</t>
         </is>
       </c>
       <c r="F59" s="24" t="inlineStr">
@@ -20345,12 +20345,12 @@
       </c>
       <c r="D61" s="24" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E61" s="24" t="inlineStr">
         <is>
-          <t>2.5% rostered</t>
+          <t>2.4% rostered</t>
         </is>
       </c>
       <c r="F61" s="24" t="inlineStr">
@@ -20407,12 +20407,12 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>1.5% rostered</t>
+          <t>1.7% rostered</t>
         </is>
       </c>
       <c r="F62" s="13" t="inlineStr">
@@ -20787,12 +20787,12 @@
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>70.4% rostered</t>
+          <t>70.2% rostered</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
@@ -20854,12 +20854,12 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>58.2% rostered</t>
+          <t>57.9% rostered</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">
@@ -20921,12 +20921,12 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>19.4% rostered</t>
+          <t>19.3% rostered</t>
         </is>
       </c>
       <c r="G8" s="13" t="inlineStr">
@@ -20988,12 +20988,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>7.7% rostered</t>
+          <t>7.6% rostered</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -21122,12 +21122,12 @@
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t>1.8% rostered</t>
+          <t>1.7% rostered</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -21256,12 +21256,12 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>1.3%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t>1.3% rostered</t>
+          <t>1.2% rostered</t>
         </is>
       </c>
       <c r="G13" s="8" t="inlineStr">
@@ -21524,12 +21524,12 @@
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>92.8%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>92.8% rostered</t>
+          <t>92.7% rostered</t>
         </is>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -21591,12 +21591,12 @@
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>64.6% rostered</t>
+          <t>64.4% rostered</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
